--- a/src/data/COREP_files/G_EU_C_C0200.xlsx
+++ b/src/data/COREP_files/G_EU_C_C0200.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K80"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1"/>
@@ -470,6 +470,12 @@
           <t xml:space="preserve">TOTAL RISK EXPOSURE AMOUNT </t>
         </is>
       </c>
+      <c r="E6" t="n">
+        <v>49</v>
+      </c>
+      <c r="F6" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -487,6 +493,12 @@
           <t xml:space="preserve">Of which: Investment firms under Article 90 paragraph 2 and Article 93 of CRR </t>
         </is>
       </c>
+      <c r="E7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -504,6 +516,12 @@
           <t>Of which: Investment firms under Article 91 paragraph 1 and 2 and Article 92 of CRR</t>
         </is>
       </c>
+      <c r="E8" t="n">
+        <v>51</v>
+      </c>
+      <c r="F8" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -521,6 +539,12 @@
           <t>RISK WEIGHTED EXPOSURE AMOUNTS FOR CREDIT, COUNTERPARTY CREDIT AND DILUTION RISKS AND FREE DELIVERIES</t>
         </is>
       </c>
+      <c r="E9" t="n">
+        <v>52</v>
+      </c>
+      <c r="F9" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
@@ -538,6 +562,12 @@
           <t>Standardised approach (SA)</t>
         </is>
       </c>
+      <c r="E10" t="n">
+        <v>53</v>
+      </c>
+      <c r="F10" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
@@ -572,6 +602,12 @@
           <t>Central governments or central banks</t>
         </is>
       </c>
+      <c r="E12" t="n">
+        <v>55</v>
+      </c>
+      <c r="F12" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
@@ -589,6 +625,12 @@
           <t>Regional governments or local authorities</t>
         </is>
       </c>
+      <c r="E13" t="n">
+        <v>56</v>
+      </c>
+      <c r="F13" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
@@ -606,6 +648,12 @@
           <t xml:space="preserve">Public sector entities </t>
         </is>
       </c>
+      <c r="E14" t="n">
+        <v>57</v>
+      </c>
+      <c r="F14" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
@@ -674,6 +722,12 @@
           <t>Corporates</t>
         </is>
       </c>
+      <c r="E18" t="n">
+        <v>52</v>
+      </c>
+      <c r="F18" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
@@ -691,6 +745,12 @@
           <t>Retail</t>
         </is>
       </c>
+      <c r="E19" t="n">
+        <v>53</v>
+      </c>
+      <c r="F19" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
@@ -708,6 +768,12 @@
           <t>Secured by mortgages on immovable  property</t>
         </is>
       </c>
+      <c r="E20" t="n">
+        <v>54</v>
+      </c>
+      <c r="F20" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
@@ -759,6 +825,12 @@
           <t>Covered bonds</t>
         </is>
       </c>
+      <c r="E23" t="n">
+        <v>57</v>
+      </c>
+      <c r="F23" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
@@ -844,6 +916,12 @@
           <t>Securitisation positions SA</t>
         </is>
       </c>
+      <c r="E28" t="n">
+        <v>52</v>
+      </c>
+      <c r="F28" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
@@ -878,6 +956,12 @@
           <t>Internal ratings based Approach (IRB)</t>
         </is>
       </c>
+      <c r="E30" t="n">
+        <v>54</v>
+      </c>
+      <c r="F30" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
@@ -895,6 +979,12 @@
           <t>IRB approaches when neither own estimates of LGD nor Conversion Factors are used</t>
         </is>
       </c>
+      <c r="E31" t="n">
+        <v>55</v>
+      </c>
+      <c r="F31" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
@@ -912,6 +1002,12 @@
           <t>Central governments and central banks</t>
         </is>
       </c>
+      <c r="E32" t="n">
+        <v>56</v>
+      </c>
+      <c r="F32" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
@@ -929,6 +1025,12 @@
           <t>Institutions</t>
         </is>
       </c>
+      <c r="E33" t="n">
+        <v>57</v>
+      </c>
+      <c r="F33" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
@@ -963,6 +1065,12 @@
           <t>Corporates - Specialised Lending</t>
         </is>
       </c>
+      <c r="E35" t="n">
+        <v>59</v>
+      </c>
+      <c r="F35" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
@@ -980,6 +1088,12 @@
           <t>Corporates - Other</t>
         </is>
       </c>
+      <c r="E36" t="n">
+        <v>51</v>
+      </c>
+      <c r="F36" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
@@ -997,6 +1111,12 @@
           <t>IRB approaches when own estimates of LGD and/or Conversion Factors are used</t>
         </is>
       </c>
+      <c r="E37" t="n">
+        <v>52</v>
+      </c>
+      <c r="F37" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="38">
       <c r="B38" t="inlineStr">
@@ -1014,6 +1134,12 @@
           <t>Central governments and central banks</t>
         </is>
       </c>
+      <c r="E38" t="n">
+        <v>53</v>
+      </c>
+      <c r="F38" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
@@ -1031,6 +1157,12 @@
           <t>Institutions</t>
         </is>
       </c>
+      <c r="E39" t="n">
+        <v>54</v>
+      </c>
+      <c r="F39" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="40">
       <c r="B40" t="inlineStr">
@@ -1048,6 +1180,12 @@
           <t>Corporates - SME</t>
         </is>
       </c>
+      <c r="E40" t="n">
+        <v>55</v>
+      </c>
+      <c r="F40" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
@@ -1065,6 +1203,12 @@
           <t>Corporates - Specialised Lending</t>
         </is>
       </c>
+      <c r="E41" t="n">
+        <v>56</v>
+      </c>
+      <c r="F41" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="42">
       <c r="B42" t="inlineStr">
@@ -1082,6 +1226,12 @@
           <t>Corporates - Other</t>
         </is>
       </c>
+      <c r="E42" t="n">
+        <v>57</v>
+      </c>
+      <c r="F42" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
@@ -1099,6 +1249,12 @@
           <t>Retail - Secured by real estate SME</t>
         </is>
       </c>
+      <c r="E43" t="n">
+        <v>58</v>
+      </c>
+      <c r="F43" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="44">
       <c r="B44" t="inlineStr">
@@ -1133,6 +1289,12 @@
           <t>Retail - Qualifying revolving</t>
         </is>
       </c>
+      <c r="E45" t="n">
+        <v>60</v>
+      </c>
+      <c r="F45" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="46">
       <c r="B46" t="inlineStr">
@@ -1184,6 +1346,12 @@
           <t>Equity IRB</t>
         </is>
       </c>
+      <c r="E48" t="n">
+        <v>54</v>
+      </c>
+      <c r="F48" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="49">
       <c r="B49" t="inlineStr">
@@ -1235,6 +1403,12 @@
           <t>Other non credit-obligation assets</t>
         </is>
       </c>
+      <c r="E51" t="n">
+        <v>57</v>
+      </c>
+      <c r="F51" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="52">
       <c r="B52" t="inlineStr">
@@ -1320,6 +1494,12 @@
           <t>TOTAL RISK EXPOSURE AMOUNT FOR POSITION, FOREIGN EXCHANGE AND COMMODITIES RISKS</t>
         </is>
       </c>
+      <c r="E56" t="n">
+        <v>55</v>
+      </c>
+      <c r="F56" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="57">
       <c r="B57" t="inlineStr">
@@ -1439,6 +1619,12 @@
           <t>TOTAL RISK EXPOSURE AMOUNT FOR OPERATIONAL RISK (OpR )</t>
         </is>
       </c>
+      <c r="E63" t="n">
+        <v>62</v>
+      </c>
+      <c r="F63" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="64">
       <c r="B64" t="inlineStr">
@@ -1524,6 +1710,12 @@
           <t>TOTAL RISK EXPOSURE AMOUNT FOR CREDIT VALUATION ADJUSTMENT</t>
         </is>
       </c>
+      <c r="E68" t="n">
+        <v>58</v>
+      </c>
+      <c r="F68" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="69">
       <c r="B69" t="inlineStr">
@@ -1693,6 +1885,12 @@
         <is>
           <t>Of which: due to intra financial sector exposures</t>
         </is>
+      </c>
+      <c r="E78" t="n">
+        <v>59</v>
+      </c>
+      <c r="F78" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="79">
